--- a/data/results/hr_logger_1hz_analysis.xlsx
+++ b/data/results/hr_logger_1hz_analysis.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_projects\esp32_wifi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_projects\Git\motion-aware-hr-monitor\data\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20592254-750D-4C30-9EB2-1188C19BD42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93FD78FB-F30C-40B8-ACD3-216BBB6F4C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="48">
   <si>
-    <t>sample_id</t>
-  </si>
-  <si>
     <t>hr_fft</t>
   </si>
   <si>
@@ -178,6 +175,9 @@
   </si>
   <si>
     <t>This workbook contains 60 samples (positions 20-79 from original data).</t>
+  </si>
+  <si>
+    <t>seconds</t>
   </si>
 </sst>
 </file>
@@ -563,7 +563,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DataTable_1Hz" displayName="DataTable_1Hz" ref="A1:Q61">
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="sample_id"/>
+    <tableColumn id="1" xr3:uid="{B5095A7C-4710-4E73-A4EA-932FFB56BFA3}" name="seconds">
+      <calculatedColumnFormula>ROW()-ROW($A$2)</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="hr_fft"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="conf_fft"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="peak_hz"/>
@@ -757,61 +759,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="14.65" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
+      <c r="A1" t="s">
+        <v>47</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="2" spans="1:17">
-      <c r="A2" s="3">
-        <v>148</v>
+      <c r="A2">
+        <f>ROW()-ROW($A$2)</f>
+        <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>86</v>
@@ -835,7 +838,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" s="3">
         <v>0.9</v>
@@ -865,8 +868,9 @@
       </c>
     </row>
     <row r="3" spans="1:17">
-      <c r="A3" s="3">
-        <v>149</v>
+      <c r="A3">
+        <f>ROW()-ROW($A$2)</f>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>85.2</v>
@@ -890,7 +894,7 @@
         <v>0.53</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3">
         <v>0.9</v>
@@ -920,8 +924,9 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="3">
-        <v>150</v>
+      <c r="A4">
+        <f>ROW()-ROW($A$2)</f>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>82.1</v>
@@ -945,7 +950,7 @@
         <v>0.41</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J4" s="3">
         <v>0.92</v>
@@ -975,8 +980,9 @@
       </c>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="3">
-        <v>152</v>
+      <c r="A5">
+        <f>ROW()-ROW($A$2)</f>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>82.1</v>
@@ -1000,7 +1006,7 @@
         <v>0.62</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" s="3">
         <v>0.89</v>
@@ -1030,8 +1036,9 @@
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="3">
-        <v>153</v>
+      <c r="A6">
+        <f>ROW()-ROW($A$2)</f>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>80.099999999999994</v>
@@ -1055,7 +1062,7 @@
         <v>0.69</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" s="3">
         <v>0.92</v>
@@ -1085,8 +1092,9 @@
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="3">
-        <v>154</v>
+      <c r="A7">
+        <f>ROW()-ROW($A$2)</f>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>79.400000000000006</v>
@@ -1110,7 +1118,7 @@
         <v>0.72</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" s="3">
         <v>0.91</v>
@@ -1140,8 +1148,9 @@
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="3">
-        <v>155</v>
+      <c r="A8">
+        <f>ROW()-ROW($A$2)</f>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>78.5</v>
@@ -1165,7 +1174,7 @@
         <v>0.73</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" s="3">
         <v>0.92</v>
@@ -1195,8 +1204,9 @@
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="3">
-        <v>156</v>
+      <c r="A9">
+        <f>ROW()-ROW($A$2)</f>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
         <v>77.900000000000006</v>
@@ -1220,7 +1230,7 @@
         <v>0.68</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" s="3">
         <v>0.9</v>
@@ -1250,8 +1260,9 @@
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="3">
-        <v>157</v>
+      <c r="A10">
+        <f>ROW()-ROW($A$2)</f>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <v>77.3</v>
@@ -1275,7 +1286,7 @@
         <v>0.5</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" s="3">
         <v>0.94</v>
@@ -1305,8 +1316,9 @@
       </c>
     </row>
     <row r="11" spans="1:17">
-      <c r="A11" s="3">
-        <v>158</v>
+      <c r="A11">
+        <f>ROW()-ROW($A$2)</f>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
         <v>76.099999999999994</v>
@@ -1330,7 +1342,7 @@
         <v>0.31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J11" s="3">
         <v>0.92</v>
@@ -1360,8 +1372,9 @@
       </c>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="3">
-        <v>159</v>
+      <c r="A12">
+        <f>ROW()-ROW($A$2)</f>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <v>75.8</v>
@@ -1385,7 +1398,7 @@
         <v>0.47</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" s="3">
         <v>0.92</v>
@@ -1415,8 +1428,9 @@
       </c>
     </row>
     <row r="13" spans="1:17">
-      <c r="A13" s="3">
-        <v>160</v>
+      <c r="A13">
+        <f>ROW()-ROW($A$2)</f>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>75.900000000000006</v>
@@ -1440,7 +1454,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" s="3">
         <v>0.87</v>
@@ -1470,8 +1484,9 @@
       </c>
     </row>
     <row r="14" spans="1:17">
-      <c r="A14" s="3">
-        <v>161</v>
+      <c r="A14">
+        <f>ROW()-ROW($A$2)</f>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
         <v>74.2</v>
@@ -1495,7 +1510,7 @@
         <v>0.63</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" s="3">
         <v>0.92</v>
@@ -1525,8 +1540,9 @@
       </c>
     </row>
     <row r="15" spans="1:17">
-      <c r="A15" s="3">
-        <v>162</v>
+      <c r="A15">
+        <f>ROW()-ROW($A$2)</f>
+        <v>13</v>
       </c>
       <c r="B15" s="3">
         <v>73.3</v>
@@ -1550,7 +1566,7 @@
         <v>0.59</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" s="3">
         <v>0.91</v>
@@ -1580,8 +1596,9 @@
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="3">
-        <v>163</v>
+      <c r="A16">
+        <f>ROW()-ROW($A$2)</f>
+        <v>14</v>
       </c>
       <c r="B16" s="3">
         <v>73.2</v>
@@ -1605,7 +1622,7 @@
         <v>0.66</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" s="3">
         <v>0.88</v>
@@ -1635,8 +1652,9 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="3">
-        <v>164</v>
+      <c r="A17">
+        <f>ROW()-ROW($A$2)</f>
+        <v>15</v>
       </c>
       <c r="B17" s="3">
         <v>74.099999999999994</v>
@@ -1660,7 +1678,7 @@
         <v>0.48</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" s="3">
         <v>0.88</v>
@@ -1690,8 +1708,9 @@
       </c>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="3">
-        <v>165</v>
+      <c r="A18">
+        <f>ROW()-ROW($A$2)</f>
+        <v>16</v>
       </c>
       <c r="B18" s="3">
         <v>75.7</v>
@@ -1715,7 +1734,7 @@
         <v>0.6</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J18" s="3">
         <v>0.9</v>
@@ -1745,8 +1764,9 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="3">
-        <v>168</v>
+      <c r="A19">
+        <f>ROW()-ROW($A$2)</f>
+        <v>17</v>
       </c>
       <c r="B19" s="3">
         <v>81.099999999999994</v>
@@ -1770,7 +1790,7 @@
         <v>0.74</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" s="3">
         <v>0.86</v>
@@ -1800,8 +1820,9 @@
       </c>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="3">
-        <v>169</v>
+      <c r="A20">
+        <f>ROW()-ROW($A$2)</f>
+        <v>18</v>
       </c>
       <c r="B20" s="3">
         <v>80.5</v>
@@ -1825,7 +1846,7 @@
         <v>0.53</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" s="3">
         <v>0.91</v>
@@ -1855,8 +1876,9 @@
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="3">
-        <v>172</v>
+      <c r="A21">
+        <f>ROW()-ROW($A$2)</f>
+        <v>19</v>
       </c>
       <c r="B21" s="3">
         <v>76.8</v>
@@ -1880,7 +1902,7 @@
         <v>0.45</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" s="3">
         <v>0.84</v>
@@ -1910,8 +1932,9 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="A22" s="3">
-        <v>173</v>
+      <c r="A22">
+        <f>ROW()-ROW($A$2)</f>
+        <v>20</v>
       </c>
       <c r="B22" s="3">
         <v>76.599999999999994</v>
@@ -1935,7 +1958,7 @@
         <v>0.36</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" s="3">
         <v>0.86</v>
@@ -1965,8 +1988,9 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="A23" s="3">
-        <v>175</v>
+      <c r="A23">
+        <f>ROW()-ROW($A$2)</f>
+        <v>21</v>
       </c>
       <c r="B23" s="3">
         <v>77.2</v>
@@ -1990,7 +2014,7 @@
         <v>0.49</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" s="3">
         <v>0.9</v>
@@ -2020,8 +2044,9 @@
       </c>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="3">
-        <v>176</v>
+      <c r="A24">
+        <f>ROW()-ROW($A$2)</f>
+        <v>22</v>
       </c>
       <c r="B24" s="3">
         <v>78.2</v>
@@ -2045,7 +2070,7 @@
         <v>0.51</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J24" s="3">
         <v>0.92</v>
@@ -2075,8 +2100,9 @@
       </c>
     </row>
     <row r="25" spans="1:17">
-      <c r="A25" s="3">
-        <v>177</v>
+      <c r="A25">
+        <f>ROW()-ROW($A$2)</f>
+        <v>23</v>
       </c>
       <c r="B25" s="3">
         <v>78.400000000000006</v>
@@ -2100,7 +2126,7 @@
         <v>0.4</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J25" s="3">
         <v>0.9</v>
@@ -2130,8 +2156,9 @@
       </c>
     </row>
     <row r="26" spans="1:17">
-      <c r="A26" s="3">
-        <v>180</v>
+      <c r="A26">
+        <f>ROW()-ROW($A$2)</f>
+        <v>24</v>
       </c>
       <c r="B26" s="3">
         <v>78</v>
@@ -2155,7 +2182,7 @@
         <v>0.72</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J26" s="3">
         <v>0.88</v>
@@ -2185,8 +2212,9 @@
       </c>
     </row>
     <row r="27" spans="1:17">
-      <c r="A27" s="3">
-        <v>181</v>
+      <c r="A27">
+        <f>ROW()-ROW($A$2)</f>
+        <v>25</v>
       </c>
       <c r="B27" s="3">
         <v>78.7</v>
@@ -2210,7 +2238,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J27" s="3">
         <v>0.87</v>
@@ -2240,8 +2268,9 @@
       </c>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="3">
-        <v>182</v>
+      <c r="A28">
+        <f>ROW()-ROW($A$2)</f>
+        <v>26</v>
       </c>
       <c r="B28" s="3">
         <v>80</v>
@@ -2265,7 +2294,7 @@
         <v>0.68</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" s="3">
         <v>0.86</v>
@@ -2295,8 +2324,9 @@
       </c>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="3">
-        <v>183</v>
+      <c r="A29">
+        <f>ROW()-ROW($A$2)</f>
+        <v>27</v>
       </c>
       <c r="B29" s="3">
         <v>81.2</v>
@@ -2320,7 +2350,7 @@
         <v>0.88</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" s="3">
         <v>0.87</v>
@@ -2350,8 +2380,9 @@
       </c>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="3">
-        <v>184</v>
+      <c r="A30">
+        <f>ROW()-ROW($A$2)</f>
+        <v>28</v>
       </c>
       <c r="B30" s="3">
         <v>82</v>
@@ -2375,7 +2406,7 @@
         <v>0.88</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J30" s="3">
         <v>0.9</v>
@@ -2405,8 +2436,9 @@
       </c>
     </row>
     <row r="31" spans="1:17">
-      <c r="A31" s="3">
-        <v>185</v>
+      <c r="A31">
+        <f>ROW()-ROW($A$2)</f>
+        <v>29</v>
       </c>
       <c r="B31" s="3">
         <v>82.1</v>
@@ -2430,7 +2462,7 @@
         <v>0.66</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J31" s="3">
         <v>0.91</v>
@@ -2460,8 +2492,9 @@
       </c>
     </row>
     <row r="32" spans="1:17">
-      <c r="A32" s="3">
-        <v>186</v>
+      <c r="A32">
+        <f>ROW()-ROW($A$2)</f>
+        <v>30</v>
       </c>
       <c r="B32" s="3">
         <v>80.8</v>
@@ -2485,7 +2518,7 @@
         <v>0.59</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" s="3">
         <v>0.84</v>
@@ -2515,8 +2548,9 @@
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="3">
-        <v>187</v>
+      <c r="A33">
+        <f>ROW()-ROW($A$2)</f>
+        <v>31</v>
       </c>
       <c r="B33" s="3">
         <v>79.2</v>
@@ -2540,7 +2574,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" s="3">
         <v>0.92</v>
@@ -2570,8 +2604,9 @@
       </c>
     </row>
     <row r="34" spans="1:17">
-      <c r="A34" s="3">
-        <v>188</v>
+      <c r="A34">
+        <f>ROW()-ROW($A$2)</f>
+        <v>32</v>
       </c>
       <c r="B34" s="3">
         <v>79.7</v>
@@ -2595,7 +2630,7 @@
         <v>0.64</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J34" s="3">
         <v>0.9</v>
@@ -2625,8 +2660,9 @@
       </c>
     </row>
     <row r="35" spans="1:17">
-      <c r="A35" s="3">
-        <v>189</v>
+      <c r="A35">
+        <f>ROW()-ROW($A$2)</f>
+        <v>33</v>
       </c>
       <c r="B35" s="3">
         <v>80.3</v>
@@ -2650,7 +2686,7 @@
         <v>0.49</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J35" s="3">
         <v>0.92</v>
@@ -2680,8 +2716,9 @@
       </c>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="3">
-        <v>190</v>
+      <c r="A36">
+        <f>ROW()-ROW($A$2)</f>
+        <v>34</v>
       </c>
       <c r="B36" s="3">
         <v>80.400000000000006</v>
@@ -2705,7 +2742,7 @@
         <v>0.7</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J36" s="3">
         <v>0.85</v>
@@ -2735,8 +2772,9 @@
       </c>
     </row>
     <row r="37" spans="1:17">
-      <c r="A37" s="3">
-        <v>191</v>
+      <c r="A37">
+        <f>ROW()-ROW($A$2)</f>
+        <v>35</v>
       </c>
       <c r="B37" s="3">
         <v>80.7</v>
@@ -2760,7 +2798,7 @@
         <v>0.52</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" s="3">
         <v>0.89</v>
@@ -2790,8 +2828,9 @@
       </c>
     </row>
     <row r="38" spans="1:17">
-      <c r="A38" s="3">
-        <v>192</v>
+      <c r="A38">
+        <f>ROW()-ROW($A$2)</f>
+        <v>36</v>
       </c>
       <c r="B38" s="3">
         <v>81</v>
@@ -2815,7 +2854,7 @@
         <v>0.64</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J38" s="3">
         <v>0.88</v>
@@ -2845,8 +2884,9 @@
       </c>
     </row>
     <row r="39" spans="1:17">
-      <c r="A39" s="3">
-        <v>193</v>
+      <c r="A39">
+        <f>ROW()-ROW($A$2)</f>
+        <v>37</v>
       </c>
       <c r="B39" s="3">
         <v>81</v>
@@ -2870,7 +2910,7 @@
         <v>0.59</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J39" s="3">
         <v>0.87</v>
@@ -2900,8 +2940,9 @@
       </c>
     </row>
     <row r="40" spans="1:17">
-      <c r="A40" s="3">
-        <v>194</v>
+      <c r="A40">
+        <f>ROW()-ROW($A$2)</f>
+        <v>38</v>
       </c>
       <c r="B40" s="3">
         <v>80.400000000000006</v>
@@ -2925,7 +2966,7 @@
         <v>0.61</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J40" s="3">
         <v>0.9</v>
@@ -2955,8 +2996,9 @@
       </c>
     </row>
     <row r="41" spans="1:17">
-      <c r="A41" s="3">
-        <v>195</v>
+      <c r="A41">
+        <f>ROW()-ROW($A$2)</f>
+        <v>39</v>
       </c>
       <c r="B41" s="3">
         <v>79.3</v>
@@ -2980,7 +3022,7 @@
         <v>0.62</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J41" s="3">
         <v>0.93</v>
@@ -3010,8 +3052,9 @@
       </c>
     </row>
     <row r="42" spans="1:17">
-      <c r="A42" s="3">
-        <v>196</v>
+      <c r="A42">
+        <f>ROW()-ROW($A$2)</f>
+        <v>40</v>
       </c>
       <c r="B42" s="3">
         <v>79</v>
@@ -3035,7 +3078,7 @@
         <v>0.73</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J42" s="3">
         <v>0.86</v>
@@ -3065,8 +3108,9 @@
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="3">
-        <v>199</v>
+      <c r="A43">
+        <f>ROW()-ROW($A$2)</f>
+        <v>41</v>
       </c>
       <c r="B43" s="3">
         <v>79.7</v>
@@ -3090,7 +3134,7 @@
         <v>0.73</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J43" s="3">
         <v>0.94</v>
@@ -3120,8 +3164,9 @@
       </c>
     </row>
     <row r="44" spans="1:17">
-      <c r="A44" s="3">
-        <v>200</v>
+      <c r="A44">
+        <f>ROW()-ROW($A$2)</f>
+        <v>42</v>
       </c>
       <c r="B44" s="3">
         <v>80.900000000000006</v>
@@ -3145,7 +3190,7 @@
         <v>0.65</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J44" s="3">
         <v>0.85</v>
@@ -3175,8 +3220,9 @@
       </c>
     </row>
     <row r="45" spans="1:17">
-      <c r="A45" s="3">
-        <v>201</v>
+      <c r="A45">
+        <f>ROW()-ROW($A$2)</f>
+        <v>43</v>
       </c>
       <c r="B45" s="3">
         <v>81.5</v>
@@ -3200,7 +3246,7 @@
         <v>0.63</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J45" s="3">
         <v>0.89</v>
@@ -3230,8 +3276,9 @@
       </c>
     </row>
     <row r="46" spans="1:17">
-      <c r="A46" s="3">
-        <v>202</v>
+      <c r="A46">
+        <f>ROW()-ROW($A$2)</f>
+        <v>44</v>
       </c>
       <c r="B46" s="3">
         <v>81.7</v>
@@ -3255,7 +3302,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" s="3">
         <v>0.88</v>
@@ -3285,8 +3332,9 @@
       </c>
     </row>
     <row r="47" spans="1:17">
-      <c r="A47" s="3">
-        <v>203</v>
+      <c r="A47">
+        <f>ROW()-ROW($A$2)</f>
+        <v>45</v>
       </c>
       <c r="B47" s="3">
         <v>81.7</v>
@@ -3310,7 +3358,7 @@
         <v>0.72</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J47" s="3">
         <v>0.89</v>
@@ -3340,8 +3388,9 @@
       </c>
     </row>
     <row r="48" spans="1:17">
-      <c r="A48" s="3">
-        <v>204</v>
+      <c r="A48">
+        <f>ROW()-ROW($A$2)</f>
+        <v>46</v>
       </c>
       <c r="B48" s="3">
         <v>81.5</v>
@@ -3365,7 +3414,7 @@
         <v>0.76</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J48" s="3">
         <v>0.9</v>
@@ -3395,8 +3444,9 @@
       </c>
     </row>
     <row r="49" spans="1:17">
-      <c r="A49" s="3">
-        <v>205</v>
+      <c r="A49">
+        <f>ROW()-ROW($A$2)</f>
+        <v>47</v>
       </c>
       <c r="B49" s="3">
         <v>81.099999999999994</v>
@@ -3420,7 +3470,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J49" s="3">
         <v>0.9</v>
@@ -3450,8 +3500,9 @@
       </c>
     </row>
     <row r="50" spans="1:17">
-      <c r="A50" s="3">
-        <v>206</v>
+      <c r="A50">
+        <f>ROW()-ROW($A$2)</f>
+        <v>48</v>
       </c>
       <c r="B50" s="3">
         <v>80.7</v>
@@ -3475,7 +3526,7 @@
         <v>0.68</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J50" s="3">
         <v>0.87</v>
@@ -3505,8 +3556,9 @@
       </c>
     </row>
     <row r="51" spans="1:17">
-      <c r="A51" s="3">
-        <v>207</v>
+      <c r="A51">
+        <f>ROW()-ROW($A$2)</f>
+        <v>49</v>
       </c>
       <c r="B51" s="3">
         <v>80.599999999999994</v>
@@ -3530,7 +3582,7 @@
         <v>0.69</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J51" s="3">
         <v>0.88</v>
@@ -3560,8 +3612,9 @@
       </c>
     </row>
     <row r="52" spans="1:17">
-      <c r="A52" s="3">
-        <v>208</v>
+      <c r="A52">
+        <f>ROW()-ROW($A$2)</f>
+        <v>50</v>
       </c>
       <c r="B52" s="3">
         <v>81</v>
@@ -3585,7 +3638,7 @@
         <v>0.68</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J52" s="3">
         <v>0.84</v>
@@ -3615,8 +3668,9 @@
       </c>
     </row>
     <row r="53" spans="1:17">
-      <c r="A53" s="3">
-        <v>209</v>
+      <c r="A53">
+        <f>ROW()-ROW($A$2)</f>
+        <v>51</v>
       </c>
       <c r="B53" s="3">
         <v>81.599999999999994</v>
@@ -3640,7 +3694,7 @@
         <v>0.74</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J53" s="3">
         <v>0.84</v>
@@ -3670,8 +3724,9 @@
       </c>
     </row>
     <row r="54" spans="1:17">
-      <c r="A54" s="3">
-        <v>210</v>
+      <c r="A54">
+        <f>ROW()-ROW($A$2)</f>
+        <v>52</v>
       </c>
       <c r="B54" s="3">
         <v>82.2</v>
@@ -3695,7 +3750,7 @@
         <v>0.53</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J54" s="3">
         <v>0.88</v>
@@ -3725,8 +3780,9 @@
       </c>
     </row>
     <row r="55" spans="1:17">
-      <c r="A55" s="3">
-        <v>211</v>
+      <c r="A55">
+        <f>ROW()-ROW($A$2)</f>
+        <v>53</v>
       </c>
       <c r="B55" s="3">
         <v>82.5</v>
@@ -3750,7 +3806,7 @@
         <v>0.7</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J55" s="3">
         <v>0.87</v>
@@ -3780,8 +3836,9 @@
       </c>
     </row>
     <row r="56" spans="1:17">
-      <c r="A56" s="3">
-        <v>212</v>
+      <c r="A56">
+        <f>ROW()-ROW($A$2)</f>
+        <v>54</v>
       </c>
       <c r="B56" s="3">
         <v>82.4</v>
@@ -3805,7 +3862,7 @@
         <v>0.52</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J56" s="3">
         <v>0.86</v>
@@ -3835,8 +3892,9 @@
       </c>
     </row>
     <row r="57" spans="1:17">
-      <c r="A57" s="3">
-        <v>213</v>
+      <c r="A57">
+        <f>ROW()-ROW($A$2)</f>
+        <v>55</v>
       </c>
       <c r="B57" s="3">
         <v>82.7</v>
@@ -3860,7 +3918,7 @@
         <v>0.52</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J57" s="3">
         <v>0.88</v>
@@ -3890,8 +3948,9 @@
       </c>
     </row>
     <row r="58" spans="1:17">
-      <c r="A58" s="3">
-        <v>214</v>
+      <c r="A58">
+        <f>ROW()-ROW($A$2)</f>
+        <v>56</v>
       </c>
       <c r="B58" s="3">
         <v>82.7</v>
@@ -3915,7 +3974,7 @@
         <v>0.64</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J58" s="3">
         <v>0.86</v>
@@ -3945,8 +4004,9 @@
       </c>
     </row>
     <row r="59" spans="1:17">
-      <c r="A59" s="3">
-        <v>215</v>
+      <c r="A59">
+        <f>ROW()-ROW($A$2)</f>
+        <v>57</v>
       </c>
       <c r="B59" s="3">
         <v>82.1</v>
@@ -3970,7 +4030,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J59" s="3">
         <v>0.85</v>
@@ -4000,8 +4060,9 @@
       </c>
     </row>
     <row r="60" spans="1:17">
-      <c r="A60" s="3">
-        <v>216</v>
+      <c r="A60">
+        <f>ROW()-ROW($A$2)</f>
+        <v>58</v>
       </c>
       <c r="B60" s="3">
         <v>81.599999999999994</v>
@@ -4025,7 +4086,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J60" s="3">
         <v>0.84</v>
@@ -4055,8 +4116,9 @@
       </c>
     </row>
     <row r="61" spans="1:17">
-      <c r="A61" s="3">
-        <v>217</v>
+      <c r="A61">
+        <f>ROW()-ROW($A$2)</f>
+        <v>59</v>
       </c>
       <c r="B61" s="3">
         <v>81.5</v>
@@ -4080,7 +4142,7 @@
         <v>0.62</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J61" s="3">
         <v>0.91</v>
@@ -4130,7 +4192,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.649999999999999" customHeight="1">
       <c r="A1" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -4138,47 +4200,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="B2">
-        <f>COUNTA(Data!A2:A61)</f>
-        <v>60</v>
+        <f>COUNTA(Data!#REF!)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="5">
         <f>AVERAGE(Data!Q2:Q61)</f>
         <v>1.0833333333333341</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="13">
+        <f>COUNTA(Data!#REF!)</f>
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="13">
-        <f>COUNTA(Data!A2:A61)</f>
-        <v>60</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="F4" t="s">
         <v>25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>26</v>
       </c>
       <c r="G4">
         <f>B5</f>
@@ -4187,20 +4249,20 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="13">
         <f>AVERAGE(Data!Q2:Q61)</f>
         <v>1.0833333333333341</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="F5" t="s">
         <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
       </c>
       <c r="G5">
         <f>B6</f>
@@ -4209,20 +4271,20 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="13">
         <f>SQRT(SUMPRODUCT(Data!P2:P61,Data!P2:P61)/COUNTA(Data!P2:P61))</f>
         <v>1.5273069981724929</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" t="s">
-        <v>31</v>
       </c>
       <c r="G6">
         <f>B7</f>
@@ -4231,102 +4293,102 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="13">
         <f>MAX(Data!Q2:Q61)</f>
         <v>5.9000000000000057</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="13">
         <f>_xlfn.STDEV.S(Data!G2:G61)</f>
         <v>2.6921606217979113</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="15">
         <f>COUNTIF(Data!I2:I61,"HOLD")/COUNTA(Data!I2:I61)*100</f>
         <v>0</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>36</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="13">
         <f>AVERAGE(Data!H2:H61)</f>
         <v>0.60499999999999998</v>
       </c>
       <c r="C10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="13">
         <f>AVERAGE(Data!O2:O61)</f>
         <v>80.233333333333334</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="14">
         <f>AVERAGE(Data!G2:G61)</f>
         <v>79.819999999999979</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4334,7 +4396,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="19"/>
       <c r="C17" s="19"/>
